--- a/data/trans_orig/IP07C05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C05-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  triste en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de sentirse triste en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>20531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>20515</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20936</t>
+          <t>20917</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36701</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>28068</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43996</t>
+          <t>44268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26543</t>
+          <t>26548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42377</t>
+          <t>42804</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58652</t>
+          <t>59215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80463</t>
+          <t>81010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50399</t>
+          <t>51013</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67223</t>
+          <t>68269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66131</t>
+          <t>66324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83756</t>
+          <t>84117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>122583</t>
+          <t>122183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147228</t>
+          <t>145505</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>9768</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17745</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32460</t>
+          <t>32197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11292</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24339</t>
+          <t>23917</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32124</t>
+          <t>31881</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51894</t>
+          <t>51060</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30964</t>
+          <t>30878</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49449</t>
+          <t>49189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31440</t>
+          <t>31591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49104</t>
+          <t>49511</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67672</t>
+          <t>67916</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93291</t>
+          <t>93401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97508</t>
+          <t>98326</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118591</t>
+          <t>118890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115156</t>
+          <t>115177</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134526</t>
+          <t>135140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218495</t>
+          <t>219169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>247673</t>
+          <t>248642</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,48%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>488</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30262</t>
+          <t>30828</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49014</t>
+          <t>49216</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23304</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39896</t>
+          <t>40169</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58101</t>
+          <t>56219</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>82982</t>
+          <t>82463</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63627</t>
+          <t>64658</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88073</t>
+          <t>88139</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62703</t>
+          <t>63137</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87159</t>
+          <t>87848</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>132883</t>
+          <t>133695</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>168515</t>
+          <t>168752</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154087</t>
+          <t>154549</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180241</t>
+          <t>180259</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186682</t>
+          <t>186257</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>213346</t>
+          <t>212644</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>348536</t>
+          <t>348355</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>385780</t>
+          <t>385785</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  triste en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse triste en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>35762</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26572</t>
+          <t>26757</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43884</t>
+          <t>44118</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52080</t>
+          <t>51572</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75640</t>
+          <t>74811</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33830</t>
+          <t>33351</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52294</t>
+          <t>51740</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42946</t>
+          <t>41712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61473</t>
+          <t>61918</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80977</t>
+          <t>80393</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106472</t>
+          <t>107990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60368</t>
+          <t>61062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82550</t>
+          <t>82269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55651</t>
+          <t>55912</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76804</t>
+          <t>76211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>123341</t>
+          <t>122412</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151327</t>
+          <t>151243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,52%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26614</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44096</t>
+          <t>43503</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22382</t>
+          <t>22940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>39007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>53489</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>75959</t>
+          <t>76944</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46866</t>
+          <t>45738</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66382</t>
+          <t>66263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40220</t>
+          <t>40489</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59291</t>
+          <t>60120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90444</t>
+          <t>93044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118530</t>
+          <t>119380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56415</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77919</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74483</t>
+          <t>74770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97278</t>
+          <t>96474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>139132</t>
+          <t>138583</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168716</t>
+          <t>168387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>13045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50587</t>
+          <t>49945</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74691</t>
+          <t>73421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53156</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76048</t>
+          <t>78356</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>110361</t>
+          <t>109637</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143981</t>
+          <t>146016</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84006</t>
+          <t>85220</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>112037</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86767</t>
+          <t>88411</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>114854</t>
+          <t>115306</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>180477</t>
+          <t>177593</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>219074</t>
+          <t>219497</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124094</t>
+          <t>124169</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153226</t>
+          <t>151750</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137260</t>
+          <t>137110</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166767</t>
+          <t>165951</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>270628</t>
+          <t>269591</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>311839</t>
+          <t>311060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  triste en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse triste en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31285</t>
+          <t>30972</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16388</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31703</t>
+          <t>31582</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36911</t>
+          <t>37018</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58333</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43653</t>
+          <t>44083</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61892</t>
+          <t>63163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46593</t>
+          <t>48162</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67856</t>
+          <t>68759</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96039</t>
+          <t>96046</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125260</t>
+          <t>124578</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90042</t>
+          <t>89424</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111166</t>
+          <t>111153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81636</t>
+          <t>82783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105221</t>
+          <t>104667</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179042</t>
+          <t>178396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209732</t>
+          <t>211636</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26763</t>
+          <t>26980</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44402</t>
+          <t>43917</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29072</t>
+          <t>28952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>45232</t>
+          <t>45784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68186</t>
+          <t>69372</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50427</t>
+          <t>50017</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71044</t>
+          <t>71130</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51464</t>
+          <t>51883</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72616</t>
+          <t>72392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106834</t>
+          <t>108253</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137044</t>
+          <t>137725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,06%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52486</t>
+          <t>52747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74877</t>
+          <t>75121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75069</t>
+          <t>75887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97842</t>
+          <t>97221</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134173</t>
+          <t>135068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163823</t>
+          <t>164952</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>47664</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71346</t>
+          <t>71415</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35457</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56786</t>
+          <t>56614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>87486</t>
+          <t>87960</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>118492</t>
+          <t>118842</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99111</t>
+          <t>100142</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>128520</t>
+          <t>128006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>104216</t>
+          <t>105434</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>134083</t>
+          <t>134358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>213321</t>
+          <t>212435</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>255414</t>
+          <t>255096</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148101</t>
+          <t>148667</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179895</t>
+          <t>179183</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>163112</t>
+          <t>163627</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>195184</t>
+          <t>194537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>321411</t>
+          <t>321812</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>365290</t>
+          <t>365179</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  triste en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de sentirse triste en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7561,12 +7561,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7646,12 +7646,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>905</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13650</t>
+          <t>14617</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14118</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29539</t>
+          <t>30146</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18026</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30704</t>
+          <t>30773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>18179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34034</t>
+          <t>33886</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>39468</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59983</t>
+          <t>60840</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26649</t>
+          <t>25673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40094</t>
+          <t>40347</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48096</t>
+          <t>48111</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65458</t>
+          <t>65483</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77437</t>
+          <t>77728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101783</t>
+          <t>101446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>527</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19104</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43675</t>
+          <t>45316</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25515</t>
+          <t>24545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57556</t>
+          <t>55324</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>21267</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>52733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>37004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63445</t>
+          <t>64079</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66767</t>
+          <t>67438</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109968</t>
+          <t>111393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72548</t>
+          <t>73902</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112739</t>
+          <t>113326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76642</t>
+          <t>76244</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>110324</t>
+          <t>111229</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156985</t>
+          <t>157130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>214809</t>
+          <t>213646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,75%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28951</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27413</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57540</t>
+          <t>59010</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43564</t>
+          <t>42691</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78920</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39723</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78182</t>
+          <t>77187</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60667</t>
+          <t>60757</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91262</t>
+          <t>91568</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111479</t>
+          <t>112537</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160231</t>
+          <t>160536</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>103589</t>
+          <t>105315</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155894</t>
+          <t>157684</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>132144</t>
+          <t>131434</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>170443</t>
+          <t>170829</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>246457</t>
+          <t>245352</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>310916</t>
+          <t>313463</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
